--- a/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
@@ -393,7 +393,7 @@
         <v>0.001</v>
       </c>
       <c r="B2">
-        <v>0.9952168051532214</v>
+        <v>0.9910715690351823</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>0.002</v>
       </c>
       <c r="B3">
-        <v>0.9904772252582027</v>
+        <v>0.982297195199237</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>7.2</v>
       </c>
       <c r="B4">
-        <v>0.02212904569701777</v>
+        <v>0.01279949381076153</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>28</v>
       </c>
       <c r="B5">
-        <v>0.005140972957584596</v>
+        <v>0.003098069296142029</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>0.003070558120474542</v>
+        <v>0.001882203438645531</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>86</v>
       </c>
       <c r="B7">
-        <v>0.001516464065353579</v>
+        <v>0.000952374230342574</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>150</v>
       </c>
       <c r="B8">
-        <v>0.0008264898334248372</v>
+        <v>0.0005302459606930636</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>200</v>
       </c>
       <c r="B9">
-        <v>0.0006037037244144665</v>
+        <v>0.0003916547987149594</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>220</v>
       </c>
       <c r="B10">
-        <v>0.0005440251315709608</v>
+        <v>0.0003542479004025431</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>250</v>
       </c>
       <c r="B11">
-        <v>0.0004731312643531973</v>
+        <v>0.0003096215177968283</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>280</v>
       </c>
       <c r="B12">
-        <v>0.0004180407796212915</v>
+        <v>0.0002747812363092989</v>
       </c>
     </row>
   </sheetData>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,89 +390,81 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.9910715690351823</v>
+        <v>0.9172041691225635</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.002</v>
+        <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.982297195199237</v>
+        <v>0.01279949381076153</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>0.01279949381076153</v>
+        <v>0.003098069296142029</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B5">
-        <v>0.003098069296142029</v>
+        <v>0.001882203438645531</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B6">
-        <v>0.001882203438645531</v>
+        <v>0.000952374230342574</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B7">
-        <v>0.000952374230342574</v>
+        <v>0.0005302459606930636</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B8">
-        <v>0.0005302459606930636</v>
+        <v>0.0003916547987149594</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B9">
-        <v>0.0003916547987149594</v>
+        <v>0.0003542479004025431</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="B10">
-        <v>0.0003542479004025431</v>
+        <v>0.0003096215177968283</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B11">
-        <v>0.0003096215177968283</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>280</v>
-      </c>
-      <c r="B12">
         <v>0.0002747812363092989</v>
       </c>
     </row>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
@@ -393,7 +393,7 @@
         <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.9172041691225635</v>
+        <v>0.8594044810401683</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.01279949381076153</v>
+        <v>0.007472801190240626</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>28</v>
       </c>
       <c r="B4">
-        <v>0.003098069296142029</v>
+        <v>0.001851572823087372</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>45</v>
       </c>
       <c r="B5">
-        <v>0.001882203438645531</v>
+        <v>0.001135589253560032</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>86</v>
       </c>
       <c r="B6">
-        <v>0.000952374230342574</v>
+        <v>0.000582319971139508</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>150</v>
       </c>
       <c r="B7">
-        <v>0.0005302459606930636</v>
+        <v>0.0003280319599882583</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>200</v>
       </c>
       <c r="B8">
-        <v>0.0003916547987149594</v>
+        <v>0.0002437779286262874</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>220</v>
       </c>
       <c r="B9">
-        <v>0.0003542479004025431</v>
+        <v>0.0002209425359856459</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>250</v>
       </c>
       <c r="B10">
-        <v>0.0003096215177968283</v>
+        <v>0.0001936362162571785</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>280</v>
       </c>
       <c r="B11">
-        <v>0.0002747812363092989</v>
+        <v>0.0001722634086180085</v>
       </c>
     </row>
   </sheetData>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -398,73 +398,217 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>7.2</v>
+        <v>0.04</v>
       </c>
       <c r="B3">
-        <v>0.007472801190240626</v>
+        <v>0.6029871263659524</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>28</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="B4">
-        <v>0.001851572823087372</v>
+        <v>0.4634026447911531</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>45</v>
+        <v>0.08</v>
       </c>
       <c r="B5">
-        <v>0.001135589253560032</v>
+        <v>0.4300486291612987</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>86</v>
+        <v>0.1</v>
       </c>
       <c r="B6">
-        <v>0.000582319971139508</v>
+        <v>0.3757755433502055</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>150</v>
+        <v>0.4</v>
       </c>
       <c r="B7">
-        <v>0.0003280319599882583</v>
+        <v>0.1280432110451531</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>200</v>
+        <v>0.7</v>
       </c>
       <c r="B8">
-        <v>0.0002437779286262874</v>
+        <v>0.07647339780724841</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>0.0002209425359856459</v>
+        <v>0.05431225618506928</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="B10">
-        <v>0.0001936362162571785</v>
+        <v>0.01361062787602926</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>0.007691322389033577</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.005337135165461502</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>0.001851572823087372</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>40</v>
+      </c>
+      <c r="B14">
+        <v>0.001282168873004006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>45</v>
+      </c>
+      <c r="B15">
+        <v>0.001135589253560032</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>70</v>
+      </c>
+      <c r="B16">
+        <v>0.0007200633024848703</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>86</v>
+      </c>
+      <c r="B17">
+        <v>0.000582319971139508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>100</v>
+      </c>
+      <c r="B18">
+        <v>0.0004984175336785841</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>120</v>
+      </c>
+      <c r="B19">
+        <v>0.000412957220595775</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>150</v>
+      </c>
+      <c r="B20">
+        <v>0.0003280319599882583</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>170</v>
+      </c>
+      <c r="B21">
+        <v>0.000288288457553622</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>190</v>
+      </c>
+      <c r="B22">
+        <v>0.0002570288724353808</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>200</v>
+      </c>
+      <c r="B23">
+        <v>0.0002437779286262874</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>220</v>
+      </c>
+      <c r="B24">
+        <v>0.0002209425359856459</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>240</v>
+      </c>
+      <c r="B25">
+        <v>0.0002019679817690056</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>250</v>
+      </c>
+      <c r="B26">
+        <v>0.0001936362162571785</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>260</v>
+      </c>
+      <c r="B27">
+        <v>0.0001859551228667904</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>270</v>
+      </c>
+      <c r="B28">
+        <v>0.0001788516891796067</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
         <v>280</v>
       </c>
-      <c r="B11">
+      <c r="B29">
         <v>0.0001722634086180085</v>
       </c>
     </row>

--- a/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/bernstein_original.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -470,145 +470,177 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12">
-        <v>0.005337135165461502</v>
+        <v>0.006708732254968096</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>0.001851572823087372</v>
+        <v>0.005337135165461502</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>0.001282168873004006</v>
+        <v>0.003519466328820613</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="B15">
-        <v>0.001135589253560032</v>
+        <v>0.002618054326933769</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <v>0.0007200633024848703</v>
+        <v>0.001851572823087372</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>0.000582319971139508</v>
+        <v>0.001282168873004006</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="B18">
-        <v>0.0004984175336785841</v>
+        <v>0.001135589253560032</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="B19">
-        <v>0.000412957220595775</v>
+        <v>0.0007200633024848703</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="B20">
-        <v>0.0003280319599882583</v>
+        <v>0.000582319971139508</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="B21">
-        <v>0.000288288457553622</v>
+        <v>0.0004984175336785841</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="B22">
-        <v>0.0002570288724353808</v>
+        <v>0.000412957220595775</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B23">
-        <v>0.0002437779286262874</v>
+        <v>0.0003280319599882583</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="B24">
-        <v>0.0002209425359856459</v>
+        <v>0.000288288457553622</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="B25">
-        <v>0.0002019679817690056</v>
+        <v>0.0002570288724353808</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="B26">
-        <v>0.0001936362162571785</v>
+        <v>0.0002437779286262874</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="B27">
-        <v>0.0001859551228667904</v>
+        <v>0.0002209425359856459</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="B28">
-        <v>0.0001788516891796067</v>
+        <v>0.0002110362371906505</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
+        <v>240</v>
+      </c>
+      <c r="B29">
+        <v>0.0002019679817690056</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>250</v>
+      </c>
+      <c r="B30">
+        <v>0.0001936362162571785</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>260</v>
+      </c>
+      <c r="B31">
+        <v>0.0001859551228667904</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>270</v>
+      </c>
+      <c r="B32">
+        <v>0.0001788516891796067</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
         <v>280</v>
       </c>
-      <c r="B29">
+      <c r="B33">
         <v>0.0001722634086180085</v>
       </c>
     </row>
